--- a/docs/lift-log-program-template.xlsx
+++ b/docs/lift-log-program-template.xlsx
@@ -76,6 +76,7 @@
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -132,6 +133,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superset</t>
         </is>
       </c>
     </row>
@@ -147,6 +153,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2"/>
@@ -160,6 +167,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2"/>
@@ -173,6 +181,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2"/>
@@ -186,6 +195,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2"/>
@@ -199,6 +209,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
@@ -212,6 +223,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
@@ -225,6 +237,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2"/>
@@ -238,6 +251,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2"/>
@@ -251,6 +265,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2"/>
@@ -264,6 +279,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2"/>
@@ -277,6 +293,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2"/>
@@ -290,6 +307,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2"/>
@@ -303,6 +321,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2"/>
@@ -316,6 +335,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2"/>
@@ -329,6 +349,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2"/>
@@ -342,6 +363,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2"/>
@@ -355,6 +377,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2"/>
@@ -368,6 +391,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2"/>
@@ -381,6 +405,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2"/>
@@ -394,6 +419,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2"/>
@@ -407,6 +433,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2"/>
@@ -420,6 +447,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2"/>
@@ -433,6 +461,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2"/>
@@ -446,6 +475,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2"/>
@@ -459,6 +489,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2"/>
@@ -472,6 +503,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2"/>
@@ -485,6 +517,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2"/>
@@ -498,6 +531,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2"/>
@@ -511,6 +545,7 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="2"/>
@@ -524,6 +559,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="2"/>
@@ -537,6 +573,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="2"/>
@@ -550,6 +587,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="2"/>
@@ -563,6 +601,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2"/>
@@ -576,6 +615,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="2"/>
@@ -589,6 +629,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" s="2"/>
@@ -602,6 +643,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2"/>
@@ -615,6 +657,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="2"/>
@@ -628,6 +671,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="2"/>
@@ -641,6 +685,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="2"/>
@@ -654,6 +699,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="2"/>
@@ -667,6 +713,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" s="2"/>
@@ -680,6 +727,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="2"/>
@@ -693,6 +741,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="2"/>
@@ -706,6 +755,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="2"/>
@@ -719,6 +769,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="2"/>
@@ -732,6 +783,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="2"/>
@@ -745,6 +797,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2"/>
@@ -758,6 +811,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" s="2"/>
@@ -771,6 +825,7 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="2"/>
@@ -784,6 +839,7 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="2"/>
@@ -797,6 +853,7 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="2"/>
@@ -810,6 +867,7 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" s="2"/>
@@ -823,6 +881,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="2"/>
@@ -836,6 +895,7 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2"/>
@@ -849,6 +909,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2"/>
@@ -862,6 +923,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="2"/>
@@ -875,6 +937,7 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="2"/>
@@ -888,6 +951,7 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="2"/>
@@ -901,6 +965,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2"/>
@@ -914,6 +979,7 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="2"/>
@@ -927,6 +993,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="2"/>
@@ -940,6 +1007,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2"/>
@@ -953,6 +1021,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="2"/>
@@ -966,6 +1035,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2"/>
@@ -979,6 +1049,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2"/>
@@ -992,6 +1063,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2"/>
@@ -1005,6 +1077,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2"/>
@@ -1018,6 +1091,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2"/>
@@ -1031,6 +1105,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2"/>
@@ -1044,6 +1119,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2"/>
@@ -1057,6 +1133,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2"/>
@@ -1070,6 +1147,7 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2"/>
@@ -1083,6 +1161,7 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2"/>
@@ -1096,6 +1175,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="2"/>
@@ -1109,6 +1189,7 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2"/>
@@ -1122,6 +1203,7 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2"/>
@@ -1135,6 +1217,7 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2"/>
@@ -1148,6 +1231,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" s="2"/>
@@ -1161,6 +1245,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="2"/>
@@ -1174,6 +1259,7 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2"/>
@@ -1187,6 +1273,7 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="2"/>
@@ -1200,6 +1287,7 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" s="2"/>
@@ -1213,6 +1301,7 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" s="2"/>
@@ -1226,6 +1315,7 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" s="2"/>
@@ -1239,6 +1329,7 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2"/>
@@ -1252,6 +1343,7 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2"/>
@@ -1265,6 +1357,7 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="2"/>
@@ -1278,6 +1371,7 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2"/>
@@ -1291,6 +1385,7 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2"/>
@@ -1304,6 +1399,7 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" s="2"/>
@@ -1317,6 +1413,7 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="2"/>
@@ -1330,6 +1427,7 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="2"/>
@@ -1343,6 +1441,7 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="2"/>
@@ -1356,6 +1455,7 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2"/>
@@ -1369,6 +1469,7 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2"/>
@@ -1382,6 +1483,7 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" s="2"/>
@@ -1395,6 +1497,7 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2"/>
@@ -1408,6 +1511,7 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" s="2"/>
@@ -1421,6 +1525,7 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2"/>
@@ -1434,6 +1539,7 @@
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" s="2"/>
@@ -1447,6 +1553,7 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" s="2"/>
@@ -1460,6 +1567,7 @@
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="2"/>
@@ -1473,6 +1581,7 @@
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2"/>
@@ -1486,6 +1595,7 @@
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" s="2"/>
@@ -1499,6 +1609,7 @@
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="2"/>
@@ -1512,6 +1623,7 @@
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2"/>
@@ -1525,6 +1637,7 @@
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" s="2"/>
@@ -1538,6 +1651,7 @@
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="2"/>
@@ -1551,6 +1665,7 @@
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" s="2"/>
@@ -1564,6 +1679,7 @@
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
       <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" s="2"/>
@@ -1577,6 +1693,7 @@
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" s="2"/>
@@ -1590,6 +1707,7 @@
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" s="2"/>
@@ -1603,6 +1721,7 @@
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" s="2"/>
@@ -1616,6 +1735,7 @@
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="2"/>
@@ -1629,6 +1749,7 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2"/>
@@ -1642,6 +1763,7 @@
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2"/>
@@ -1655,6 +1777,7 @@
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="2"/>
@@ -1668,6 +1791,7 @@
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" s="2"/>
@@ -1681,6 +1805,7 @@
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2"/>
@@ -1694,6 +1819,7 @@
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2"/>
@@ -1707,6 +1833,7 @@
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" s="2"/>
@@ -1720,6 +1847,7 @@
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" s="2"/>
@@ -1733,6 +1861,7 @@
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" s="2"/>
@@ -1746,6 +1875,7 @@
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" s="2"/>
@@ -1759,6 +1889,7 @@
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" s="2"/>
@@ -1772,6 +1903,7 @@
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" s="2"/>
@@ -1785,6 +1917,7 @@
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" s="2"/>
@@ -1798,6 +1931,7 @@
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" s="2"/>
@@ -1811,6 +1945,7 @@
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" s="2"/>
@@ -1824,6 +1959,7 @@
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" s="2"/>
@@ -1837,6 +1973,7 @@
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" s="2"/>
@@ -1850,6 +1987,7 @@
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" s="2"/>
@@ -1863,6 +2001,7 @@
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" s="2"/>
@@ -1876,6 +2015,7 @@
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" s="2"/>
@@ -1889,6 +2029,7 @@
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" s="2"/>
@@ -1902,6 +2043,7 @@
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" s="2"/>
@@ -1915,6 +2057,7 @@
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" s="2"/>
@@ -1928,6 +2071,7 @@
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" s="2"/>
@@ -1941,6 +2085,7 @@
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" s="2"/>
@@ -1954,6 +2099,7 @@
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" s="2"/>
@@ -1967,6 +2113,7 @@
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" s="2"/>
@@ -1980,6 +2127,7 @@
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" s="2"/>
@@ -1993,6 +2141,7 @@
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" s="2"/>
@@ -2006,6 +2155,7 @@
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" s="2"/>
@@ -2019,6 +2169,7 @@
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" s="2"/>
@@ -2032,6 +2183,7 @@
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" s="2"/>
@@ -2045,6 +2197,7 @@
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" s="2"/>
@@ -2058,6 +2211,7 @@
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="2"/>
@@ -2071,6 +2225,7 @@
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" s="2"/>
@@ -2084,6 +2239,7 @@
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" s="2"/>
@@ -2097,6 +2253,7 @@
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" s="2"/>
@@ -2110,6 +2267,7 @@
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" s="2"/>
@@ -2123,6 +2281,7 @@
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="2"/>
@@ -2136,6 +2295,7 @@
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="2"/>
@@ -2149,6 +2309,7 @@
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="2"/>
@@ -2162,6 +2323,7 @@
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="2"/>
@@ -2175,6 +2337,7 @@
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" s="2"/>
@@ -2188,6 +2351,7 @@
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" s="2"/>
@@ -2201,6 +2365,7 @@
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" s="2"/>
@@ -2214,6 +2379,7 @@
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" s="2"/>
@@ -2227,6 +2393,7 @@
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" s="2"/>
@@ -2240,6 +2407,7 @@
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" s="2"/>
@@ -2253,6 +2421,7 @@
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" s="2"/>
@@ -2266,6 +2435,7 @@
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" s="2"/>
@@ -2279,6 +2449,7 @@
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
       <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" s="2"/>
@@ -2292,6 +2463,7 @@
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" s="2"/>
@@ -2305,6 +2477,7 @@
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" s="2"/>
@@ -2318,6 +2491,7 @@
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" s="2"/>
@@ -2331,6 +2505,7 @@
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" s="2"/>
@@ -2344,6 +2519,7 @@
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" s="2"/>
@@ -2357,6 +2533,7 @@
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" s="2"/>
@@ -2370,6 +2547,7 @@
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" s="2"/>
@@ -2383,6 +2561,7 @@
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
       <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" s="2"/>
@@ -2396,6 +2575,7 @@
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
       <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" s="2"/>
@@ -2409,6 +2589,7 @@
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" s="2"/>
@@ -2422,6 +2603,7 @@
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" s="2"/>
@@ -2435,6 +2617,7 @@
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" s="2"/>
@@ -2448,6 +2631,7 @@
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" s="2"/>
@@ -2461,6 +2645,7 @@
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" s="2"/>
@@ -2474,6 +2659,7 @@
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" s="2"/>
@@ -2487,6 +2673,7 @@
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" s="2"/>
@@ -2500,6 +2687,7 @@
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
+      <c r="L183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" s="2"/>
@@ -2513,6 +2701,7 @@
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" s="2"/>
@@ -2526,6 +2715,7 @@
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" s="2"/>
@@ -2539,6 +2729,7 @@
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" s="2"/>
@@ -2552,6 +2743,7 @@
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" s="2"/>
@@ -2565,6 +2757,7 @@
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" s="2"/>
@@ -2578,6 +2771,7 @@
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" s="2"/>
@@ -2591,6 +2785,7 @@
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
       <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" s="2"/>
@@ -2604,6 +2799,7 @@
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" s="2"/>
@@ -2617,6 +2813,7 @@
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" s="2"/>
@@ -2630,6 +2827,7 @@
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" s="2"/>
@@ -2643,6 +2841,7 @@
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" s="2"/>
@@ -2656,6 +2855,7 @@
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" s="2"/>
@@ -2669,6 +2869,7 @@
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" s="2"/>
@@ -2682,6 +2883,7 @@
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" s="2"/>
@@ -2695,6 +2897,7 @@
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" s="2"/>
@@ -2708,6 +2911,7 @@
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
       <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" s="2"/>
@@ -2721,6 +2925,7 @@
       <c r="I200" s="2"/>
       <c r="J200" s="2"/>
       <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" s="2"/>
@@ -2734,6 +2939,7 @@
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
@@ -2867,45 +3073,45 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do not rename, reorder or delete the header row - the import matches on those names.</t>
+          <t xml:space="preserve">Superset groups exercises you alternate: one set of each, then the rest, then the next round.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0"/>
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Give CONSECUTIVE rows the same letter (A, A, then B, B...). 'A1' and 'A2' also mean superset A.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Worked example</t>
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One strap double-tap ends a set and starts the next exercise of the superset straight away;</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Program   Exercise            Primary     Secondary   Sets Reps Weight MaxRPE Rest</t>
+          <t xml:space="preserve">the rest comes only after the last one. Put that rest on the LAST row of the superset -</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lower A   Leg Press midfoot   Quads       Glutes      3    10   50     8      90</t>
+          <t xml:space="preserve">the rest on the other rows of the group is not used. Leave the column blank for a normal exercise.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lower A   Lying Leg Curl      Hamstrings  Calves      3    8    30     8      90</t>
-        </is>
-      </c>
+      <c r="A24" s="0"/>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lower A   Leg Extension       Quads                   3    12   40            60</t>
+          <t xml:space="preserve">Do not rename, reorder or delete the header row - the import matches on those names.</t>
         </is>
       </c>
     </row>
@@ -2915,145 +3121,183 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muscle groups you can choose from</t>
+          <t xml:space="preserve">Worked example</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest</t>
+          <t xml:space="preserve">Program   Exercise            Primary     Secondary   Sets Reps Weight MaxRPE Rest Superset</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Front delts</t>
+          <t xml:space="preserve">Lower A   Leg Press midfoot   Quads       Glutes      3    10   50     8      90</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side delts</t>
+          <t xml:space="preserve">Lower A   Lying Leg Curl      Hamstrings  Calves      3    8    30     8           A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rear delts</t>
+          <t xml:space="preserve">Lower A   Leg Extension       Quads                   3    12   40            90   A</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triceps</t>
-        </is>
-      </c>
+      <c r="A32" s="0"/>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lats</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muscle groups you can choose from</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upper back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traps</t>
+          <t xml:space="preserve">Front delts</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Side delts</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forearms</t>
+          <t xml:space="preserve">Rear delts</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Lats</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glutes</t>
+          <t xml:space="preserve">Upper back</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adductors</t>
+          <t xml:space="preserve">Traps</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abductors</t>
+          <t xml:space="preserve">Biceps</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calves</t>
+          <t xml:space="preserve">Forearms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abs</t>
+          <t xml:space="preserve">Quads</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obliques</t>
+          <t xml:space="preserve">Hamstrings</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lower back</t>
+          <t xml:space="preserve">Glutes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adductors</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abductors</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abs</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obliques</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lower back</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Neck</t>
         </is>
